--- a/backend/app/temp/talep_listesi.xlsx
+++ b/backend/app/temp/talep_listesi.xlsx
@@ -14,12 +14,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="56">
   <si>
     <t>SATINALMA TALEP LİSTESİ</t>
   </si>
   <si>
-    <t>Rapor Tarihi: 27.04.2026 19:35</t>
+    <t>Rapor Tarihi: 30.04.2026 14:48</t>
   </si>
   <si>
     <t>Sıra</t>
@@ -37,55 +37,151 @@
     <t>Birim</t>
   </si>
   <si>
+    <t>AA001</t>
+  </si>
+  <si>
+    <t>kurşun kalem</t>
+  </si>
+  <si>
+    <t>adet</t>
+  </si>
+  <si>
+    <t>a001</t>
+  </si>
+  <si>
+    <t>silgi</t>
+  </si>
+  <si>
+    <t>a002</t>
+  </si>
+  <si>
+    <t>defter</t>
+  </si>
+  <si>
     <t>PRD-0001</t>
   </si>
   <si>
-    <t>PVC elektrik borusu 20 mm</t>
+    <t>kalem turaş</t>
+  </si>
+  <si>
+    <t>a004</t>
+  </si>
+  <si>
+    <t>pergel</t>
+  </si>
+  <si>
+    <t>a005</t>
+  </si>
+  <si>
+    <t>cetvel</t>
+  </si>
+  <si>
+    <t>a003</t>
+  </si>
+  <si>
+    <t>kalem tıraş</t>
+  </si>
+  <si>
+    <t>a006</t>
+  </si>
+  <si>
+    <t>kalem</t>
+  </si>
+  <si>
+    <t>PRD-0002</t>
+  </si>
+  <si>
+    <t>PİLOT KALEM</t>
+  </si>
+  <si>
+    <t>A102</t>
+  </si>
+  <si>
+    <t>SİLGİ BÜYÜK</t>
+  </si>
+  <si>
+    <t>A104</t>
+  </si>
+  <si>
+    <t>DOSYA KLASÖR</t>
+  </si>
+  <si>
+    <t>A105</t>
+  </si>
+  <si>
+    <t>ZIMBA MAKİNESİ</t>
+  </si>
+  <si>
+    <t>PRD-0003</t>
+  </si>
+  <si>
+    <t>Ahşap ve hafif metal montajı için uygun, galvaniz kaplı</t>
+  </si>
+  <si>
+    <t>PRD-0004</t>
+  </si>
+  <si>
+    <t>İç tesisat kablo geçişi için</t>
   </si>
   <si>
     <t>metre</t>
   </si>
   <si>
-    <t>PRD-0002</t>
-  </si>
-  <si>
-    <t>Kablo bağı 200x3.6 mm</t>
-  </si>
-  <si>
-    <t>adet</t>
-  </si>
-  <si>
-    <t>PRD-0003</t>
-  </si>
-  <si>
-    <t>Lateks eldiven</t>
+    <t>PRD-0005</t>
+  </si>
+  <si>
+    <t>Siyah, UV dayanımlı</t>
+  </si>
+  <si>
+    <t>PRD-0006</t>
+  </si>
+  <si>
+    <t>Tek kullanımlık, pudrasız</t>
   </si>
   <si>
     <t>kutu</t>
   </si>
   <si>
-    <t>PRD-0004</t>
-  </si>
-  <si>
-    <t>Akrilik mastik beyaz</t>
-  </si>
-  <si>
-    <t>PRD-0005</t>
-  </si>
-  <si>
-    <t>Spiral taşlama diski 115 mm</t>
-  </si>
-  <si>
-    <t>PRD-0006</t>
-  </si>
-  <si>
-    <t>İzolasyon bandı siyah</t>
-  </si>
-  <si>
     <t>PRD-0007</t>
   </si>
   <si>
-    <t>Temizlik bezi mikrofiber</t>
+    <t>İç cephe boşluk doldurma uygulaması</t>
+  </si>
+  <si>
+    <t>PRD-0008</t>
+  </si>
+  <si>
+    <t>Metal kesim için</t>
+  </si>
+  <si>
+    <t>PRD-0009</t>
+  </si>
+  <si>
+    <t>Elektrik bağlantı izolasyonu</t>
+  </si>
+  <si>
+    <t>PRD-0010</t>
+  </si>
+  <si>
+    <t>Genel yüzey temizliği için</t>
+  </si>
+  <si>
+    <t>A101</t>
+  </si>
+  <si>
+    <t>PİLOT KALEM MAVİ</t>
+  </si>
+  <si>
+    <t>A103</t>
+  </si>
+  <si>
+    <t>DEFTER A4</t>
+  </si>
+  <si>
+    <t>PRD-0011</t>
+  </si>
+  <si>
+    <t>uçlu kalem</t>
   </si>
 </sst>
 </file>
@@ -464,7 +560,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8.7109375" customWidth="1"/>
@@ -512,7 +608,7 @@
         <v>8</v>
       </c>
       <c r="D6" s="3">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>9</v>
@@ -529,10 +625,10 @@
         <v>11</v>
       </c>
       <c r="D7" s="3">
-        <v>500</v>
+        <v>110</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -540,16 +636,16 @@
         <v>3</v>
       </c>
       <c r="B8" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="4" t="s">
-        <v>14</v>
-      </c>
       <c r="D8" s="3">
-        <v>20</v>
+        <v>110</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -557,16 +653,16 @@
         <v>4</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D9" s="3">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -574,16 +670,16 @@
         <v>5</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D10" s="3">
-        <v>40</v>
+        <v>260</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -591,16 +687,16 @@
         <v>6</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D11" s="3">
-        <v>75</v>
+        <v>210</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -608,16 +704,288 @@
         <v>7</v>
       </c>
       <c r="B12" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D12" s="3">
+        <v>120</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="3">
+        <v>8</v>
+      </c>
+      <c r="B13" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C13" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D13" s="3">
+        <v>5</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="3">
+        <v>9</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D14" s="3">
+        <v>90</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="3">
+        <v>10</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D15" s="3">
+        <v>275</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="3">
+        <v>11</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D16" s="3">
+        <v>60</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3">
+        <v>12</v>
+      </c>
+      <c r="B17" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E12" s="3" t="s">
-        <v>12</v>
+      <c r="C17" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D17" s="3">
+        <v>40</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3">
+        <v>13</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D18" s="3">
+        <v>250</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3">
+        <v>14</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D19" s="3">
+        <v>120</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3">
+        <v>15</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D20" s="3">
+        <v>500</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3">
+        <v>16</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D21" s="3">
+        <v>20</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3">
+        <v>17</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="D22" s="3">
+        <v>36</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3">
+        <v>18</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D23" s="3">
+        <v>40</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3">
+        <v>19</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D24" s="3">
+        <v>75</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3">
+        <v>20</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D25" s="3">
+        <v>30</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3">
+        <v>21</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D26" s="3">
+        <v>410</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3">
+        <v>22</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D27" s="3">
+        <v>150</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3">
+        <v>23</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D28" s="3">
+        <v>70</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/backend/app/temp/talep_listesi.xlsx
+++ b/backend/app/temp/talep_listesi.xlsx
@@ -14,12 +14,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="36">
   <si>
     <t>SATINALMA TALEP LİSTESİ</t>
   </si>
   <si>
-    <t>Rapor Tarihi: 30.04.2026 14:48</t>
+    <t>Rapor Tarihi: 04.05.2026 20:34</t>
   </si>
   <si>
     <t>Sıra</t>
@@ -37,148 +37,88 @@
     <t>Birim</t>
   </si>
   <si>
+    <t>A101</t>
+  </si>
+  <si>
+    <t>PİLOT KALEM MAVİ</t>
+  </si>
+  <si>
+    <t>adet</t>
+  </si>
+  <si>
+    <t>A102</t>
+  </si>
+  <si>
+    <t>SİLGİ BÜYÜK</t>
+  </si>
+  <si>
+    <t>A103</t>
+  </si>
+  <si>
+    <t>DEFTER A4</t>
+  </si>
+  <si>
+    <t>a004</t>
+  </si>
+  <si>
+    <t>PERGEL</t>
+  </si>
+  <si>
+    <t>a005</t>
+  </si>
+  <si>
+    <t>CETVEL</t>
+  </si>
+  <si>
+    <t>PRD-0001</t>
+  </si>
+  <si>
+    <t>PİLOT KALEM</t>
+  </si>
+  <si>
+    <t>A104</t>
+  </si>
+  <si>
+    <t>DOSYA KLASÖR</t>
+  </si>
+  <si>
+    <t>A105</t>
+  </si>
+  <si>
+    <t>ZIMBA MAKİNESİ</t>
+  </si>
+  <si>
+    <t>a001</t>
+  </si>
+  <si>
+    <t>silgi</t>
+  </si>
+  <si>
+    <t>a002</t>
+  </si>
+  <si>
+    <t>defter</t>
+  </si>
+  <si>
+    <t>a003</t>
+  </si>
+  <si>
+    <t>kalem tıraş</t>
+  </si>
+  <si>
+    <t>a006</t>
+  </si>
+  <si>
+    <t>kalem</t>
+  </si>
+  <si>
     <t>AA001</t>
   </si>
   <si>
     <t>kurşun kalem</t>
   </si>
   <si>
-    <t>adet</t>
-  </si>
-  <si>
-    <t>a001</t>
-  </si>
-  <si>
-    <t>silgi</t>
-  </si>
-  <si>
-    <t>a002</t>
-  </si>
-  <si>
-    <t>defter</t>
-  </si>
-  <si>
-    <t>PRD-0001</t>
-  </si>
-  <si>
-    <t>kalem turaş</t>
-  </si>
-  <si>
-    <t>a004</t>
-  </si>
-  <si>
-    <t>pergel</t>
-  </si>
-  <si>
-    <t>a005</t>
-  </si>
-  <si>
-    <t>cetvel</t>
-  </si>
-  <si>
-    <t>a003</t>
-  </si>
-  <si>
-    <t>kalem tıraş</t>
-  </si>
-  <si>
-    <t>a006</t>
-  </si>
-  <si>
-    <t>kalem</t>
-  </si>
-  <si>
     <t>PRD-0002</t>
-  </si>
-  <si>
-    <t>PİLOT KALEM</t>
-  </si>
-  <si>
-    <t>A102</t>
-  </si>
-  <si>
-    <t>SİLGİ BÜYÜK</t>
-  </si>
-  <si>
-    <t>A104</t>
-  </si>
-  <si>
-    <t>DOSYA KLASÖR</t>
-  </si>
-  <si>
-    <t>A105</t>
-  </si>
-  <si>
-    <t>ZIMBA MAKİNESİ</t>
-  </si>
-  <si>
-    <t>PRD-0003</t>
-  </si>
-  <si>
-    <t>Ahşap ve hafif metal montajı için uygun, galvaniz kaplı</t>
-  </si>
-  <si>
-    <t>PRD-0004</t>
-  </si>
-  <si>
-    <t>İç tesisat kablo geçişi için</t>
-  </si>
-  <si>
-    <t>metre</t>
-  </si>
-  <si>
-    <t>PRD-0005</t>
-  </si>
-  <si>
-    <t>Siyah, UV dayanımlı</t>
-  </si>
-  <si>
-    <t>PRD-0006</t>
-  </si>
-  <si>
-    <t>Tek kullanımlık, pudrasız</t>
-  </si>
-  <si>
-    <t>kutu</t>
-  </si>
-  <si>
-    <t>PRD-0007</t>
-  </si>
-  <si>
-    <t>İç cephe boşluk doldurma uygulaması</t>
-  </si>
-  <si>
-    <t>PRD-0008</t>
-  </si>
-  <si>
-    <t>Metal kesim için</t>
-  </si>
-  <si>
-    <t>PRD-0009</t>
-  </si>
-  <si>
-    <t>Elektrik bağlantı izolasyonu</t>
-  </si>
-  <si>
-    <t>PRD-0010</t>
-  </si>
-  <si>
-    <t>Genel yüzey temizliği için</t>
-  </si>
-  <si>
-    <t>A101</t>
-  </si>
-  <si>
-    <t>PİLOT KALEM MAVİ</t>
-  </si>
-  <si>
-    <t>A103</t>
-  </si>
-  <si>
-    <t>DEFTER A4</t>
-  </si>
-  <si>
-    <t>PRD-0011</t>
   </si>
   <si>
     <t>uçlu kalem</t>
@@ -560,7 +500,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8.7109375" customWidth="1"/>
@@ -608,7 +548,7 @@
         <v>8</v>
       </c>
       <c r="D6" s="3">
-        <v>50</v>
+        <v>410</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>9</v>
@@ -625,7 +565,7 @@
         <v>11</v>
       </c>
       <c r="D7" s="3">
-        <v>110</v>
+        <v>275</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>9</v>
@@ -642,7 +582,7 @@
         <v>13</v>
       </c>
       <c r="D8" s="3">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>9</v>
@@ -659,7 +599,7 @@
         <v>15</v>
       </c>
       <c r="D9" s="3">
-        <v>40</v>
+        <v>260</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>9</v>
@@ -676,7 +616,7 @@
         <v>17</v>
       </c>
       <c r="D10" s="3">
-        <v>260</v>
+        <v>210</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>9</v>
@@ -693,7 +633,7 @@
         <v>19</v>
       </c>
       <c r="D11" s="3">
-        <v>210</v>
+        <v>90</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>9</v>
@@ -710,7 +650,7 @@
         <v>21</v>
       </c>
       <c r="D12" s="3">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>9</v>
@@ -727,7 +667,7 @@
         <v>23</v>
       </c>
       <c r="D13" s="3">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>9</v>
@@ -744,7 +684,7 @@
         <v>25</v>
       </c>
       <c r="D14" s="3">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>9</v>
@@ -761,7 +701,7 @@
         <v>27</v>
       </c>
       <c r="D15" s="3">
-        <v>275</v>
+        <v>110</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>9</v>
@@ -778,7 +718,7 @@
         <v>29</v>
       </c>
       <c r="D16" s="3">
-        <v>60</v>
+        <v>160</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>9</v>
@@ -795,7 +735,7 @@
         <v>31</v>
       </c>
       <c r="D17" s="3">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>9</v>
@@ -812,7 +752,7 @@
         <v>33</v>
       </c>
       <c r="D18" s="3">
-        <v>250</v>
+        <v>50</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>9</v>
@@ -829,162 +769,9 @@
         <v>35</v>
       </c>
       <c r="D19" s="3">
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="3">
-        <v>15</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="D20" s="3">
-        <v>500</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3">
-        <v>16</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="D21" s="3">
-        <v>20</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3">
-        <v>17</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D22" s="3">
-        <v>36</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3">
-        <v>18</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D23" s="3">
-        <v>40</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3">
-        <v>19</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D24" s="3">
-        <v>75</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3">
-        <v>20</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="D25" s="3">
-        <v>30</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3">
-        <v>21</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D26" s="3">
-        <v>410</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3">
-        <v>22</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D27" s="3">
-        <v>150</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3">
-        <v>23</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D28" s="3">
-        <v>70</v>
-      </c>
-      <c r="E28" s="3" t="s">
         <v>9</v>
       </c>
     </row>

--- a/backend/app/temp/talep_listesi.xlsx
+++ b/backend/app/temp/talep_listesi.xlsx
@@ -19,7 +19,7 @@
     <t>SATINALMA TALEP LİSTESİ</t>
   </si>
   <si>
-    <t>Rapor Tarihi: 04.05.2026 20:34</t>
+    <t>Rapor Tarihi: 05.05.2026 21:39</t>
   </si>
   <si>
     <t>Sıra</t>

--- a/backend/app/temp/talep_listesi.xlsx
+++ b/backend/app/temp/talep_listesi.xlsx
@@ -9,32 +9,95 @@
   <sheets>
     <sheet name="Talep Listesi" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Talep Listesi'!$A$11:$F$25</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="66">
+  <si>
+    <t>PROCURA AI</t>
+  </si>
+  <si>
+    <t>PROCUREMENT PLATFORM</t>
+  </si>
   <si>
     <t>SATINALMA TALEP LİSTESİ</t>
   </si>
   <si>
-    <t>Rapor Tarihi: 05.05.2026 21:39</t>
-  </si>
-  <si>
-    <t>Sıra</t>
-  </si>
-  <si>
-    <t>Ürün Kodu</t>
-  </si>
-  <si>
-    <t>Ürün Açıklaması</t>
-  </si>
-  <si>
-    <t>Talep Edilen Adet</t>
-  </si>
-  <si>
-    <t>Birim</t>
+    <t>Akıllı Satınalma &amp; Teklif Analiz Sistemi</t>
+  </si>
+  <si>
+    <t>Rapor Tarihi</t>
+  </si>
+  <si>
+    <t>07.05.2026 18:49</t>
+  </si>
+  <si>
+    <t>Rapor No: TRL-202605071849</t>
+  </si>
+  <si>
+    <t>KULLANICI FİRMASI</t>
+  </si>
+  <si>
+    <t>ASDFFG ELK. ELEKTRONİK SAN. VE TİC. LTD. ŞTİ.</t>
+  </si>
+  <si>
+    <t>Vergi No: 123 456 7890</t>
+  </si>
+  <si>
+    <t>Adres: İkitelli OSB Mah. Elektronikçiler San. Sit. No:10</t>
+  </si>
+  <si>
+    <t>TOPLAM KALEM</t>
+  </si>
+  <si>
+    <t>Ürün kalemi</t>
+  </si>
+  <si>
+    <t>TOPLAM ADET</t>
+  </si>
+  <si>
+    <t>Talep edilen adet</t>
+  </si>
+  <si>
+    <t>RAPOR TÜRÜ</t>
+  </si>
+  <si>
+    <t>Talep İcmal</t>
+  </si>
+  <si>
+    <t>Oluşturulan icmal listesi</t>
+  </si>
+  <si>
+    <t>KAYNAK</t>
+  </si>
+  <si>
+    <t>Excel, PDF, Görsel</t>
+  </si>
+  <si>
+    <t>Birleştirilmiş dokümanlar</t>
+  </si>
+  <si>
+    <t>SIRA</t>
+  </si>
+  <si>
+    <t>ÜRÜN KODU</t>
+  </si>
+  <si>
+    <t>ÜRÜN AÇIKLAMASI</t>
+  </si>
+  <si>
+    <t>TALEP EDİLEN ADET</t>
+  </si>
+  <si>
+    <t>BİRİM</t>
+  </si>
+  <si>
+    <t>AÇIKLAMA</t>
   </si>
   <si>
     <t>A101</t>
@@ -46,6 +109,9 @@
     <t>adet</t>
   </si>
   <si>
+    <t>-</t>
+  </si>
+  <si>
     <t>A102</t>
   </si>
   <si>
@@ -122,13 +188,47 @@
   </si>
   <si>
     <t>uçlu kalem</t>
+  </si>
+  <si>
+    <t>GENEL TOPLAM</t>
+  </si>
+  <si>
+    <t>RAPOR AÇIKLAMASI</t>
+  </si>
+  <si>
+    <t>Bu rapor, yüklenen Excel, PDF ve görsel dosyaların analiz edilmesi sonucunda oluşturulmuş talep icmal listesidir.
+Ürün kodu, açıklama, adet ve birim bilgileri birleştirilerek standartize edilmiştir.</t>
+  </si>
+  <si>
+    <t>SİSTEM BİLGİSİ</t>
+  </si>
+  <si>
+    <t>✓ Akıllı veri çıkarım motoru ile oluşturulmuştur.
+✓ Otomatik birleştirme ve eşleştirme yapılmıştır.
+✓ Manuel kontrol sonrası kullanılmalıdır.
+✓ Veri doğruluğu sistem tarafından ön kontrolden geçirilmiştir.</t>
+  </si>
+  <si>
+    <t>ONAY / İMZA</t>
+  </si>
+  <si>
+    <t>........................................</t>
+  </si>
+  <si>
+    <t>Ad Soyad / Unvan</t>
+  </si>
+  <si>
+    <t>🔒 CONFIDENTIAL PROCUREMENT REPORT     |     Bu belge ProcuraAI sistemi tarafından otomatik oluşturulmuştur.     |     © 2026 ProcuraAI Procurement Platform</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="3">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="#,##0"/>
+  </numFmts>
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -138,8 +238,53 @@
     </font>
     <font>
       <b/>
-      <sz val="16"/>
-      <color rgb="FF163A70"/>
+      <sz val="22"/>
+      <color rgb="FF062B5F"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <color rgb="FF062B5F"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF062B5F"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF64748B"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF0F172A"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF062B5F"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF062B5F"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -147,13 +292,58 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF062B5F"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF0F172A"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF0F172A"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0F172A"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF062B5F"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -162,12 +352,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD9E8FB"/>
+        <fgColor rgb="FF062B5F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3F7FB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -177,16 +379,46 @@
     </border>
     <border>
       <left style="thin">
-        <color auto="1"/>
+        <color rgb="FFD7DFEA"/>
       </left>
       <right style="thin">
-        <color auto="1"/>
+        <color rgb="FFD7DFEA"/>
       </right>
       <top style="thin">
-        <color auto="1"/>
+        <color rgb="FFD7DFEA"/>
       </top>
       <bottom style="thin">
-        <color auto="1"/>
+        <color rgb="FFD7DFEA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF1D4E89"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF1D4E89"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF1D4E89"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF1D4E89"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF062B5F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF062B5F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF062B5F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF062B5F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -194,17 +426,80 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -500,282 +795,524 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E19"/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8.7109375" customWidth="1"/>
     <col min="2" max="2" width="18.7109375" customWidth="1"/>
-    <col min="3" max="3" width="32.7109375" customWidth="1"/>
+    <col min="3" max="3" width="52.7109375" customWidth="1"/>
     <col min="4" max="4" width="20.7109375" customWidth="1"/>
-    <col min="5" max="5" width="12.7109375" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" customWidth="1"/>
+    <col min="6" max="6" width="36.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" t="s">
+      <c r="B1" s="1"/>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="28" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="24" customHeight="1">
+      <c r="A3" s="6" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="2" t="s">
+      <c r="B3" s="6"/>
+      <c r="F3" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="8" customHeight="1">
+      <c r="A4" s="7"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="3"/>
+      <c r="C5" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="9"/>
+      <c r="C6" s="10">
+        <v>14</v>
+      </c>
+      <c r="D6" s="10">
+        <v>2000</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="5"/>
+      <c r="C7" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="11"/>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="E11" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="13">
+        <v>1</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="D12" s="15">
+        <v>410</v>
+      </c>
+      <c r="E12" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="F12" s="14" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="16">
         <v>2</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B13" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="D13" s="18">
+        <v>275</v>
+      </c>
+      <c r="E13" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="F13" s="17" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="13">
         <v>3</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="B14" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="D14" s="15">
+        <v>150</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="F14" s="14" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="16">
         <v>4</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="B15" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="C15" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="D15" s="18">
+        <v>260</v>
+      </c>
+      <c r="E15" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="F15" s="17" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="13">
         <v>5</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="B16" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="C16" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="D16" s="15">
+        <v>210</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="F16" s="14" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="16">
         <v>6</v>
       </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="3">
-        <v>1</v>
-      </c>
-      <c r="B6" s="4" t="s">
+      <c r="B17" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="C17" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="D17" s="18">
+        <v>90</v>
+      </c>
+      <c r="E17" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="F17" s="17" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="13">
         <v>7</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="B18" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="C18" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="D18" s="15">
+        <v>60</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="F18" s="14" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" s="16">
         <v>8</v>
       </c>
-      <c r="D6" s="3">
-        <v>410</v>
-      </c>
-      <c r="E6" s="3" t="s">
+      <c r="B19" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="C19" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="D19" s="18">
+        <v>40</v>
+      </c>
+      <c r="E19" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="F19" s="17" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" s="13">
         <v>9</v>
       </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="3">
-        <v>2</v>
-      </c>
-      <c r="B7" s="4" t="s">
+      <c r="B20" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="C20" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="D20" s="15">
+        <v>110</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="F20" s="14" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" s="16">
         <v>10</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="B21" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="C21" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="D21" s="18">
+        <v>110</v>
+      </c>
+      <c r="E21" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="F21" s="17" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" s="13">
         <v>11</v>
       </c>
-      <c r="D7" s="3">
-        <v>275</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="3">
-        <v>3</v>
-      </c>
-      <c r="B8" s="4" t="s">
+      <c r="B22" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="C22" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="D22" s="15">
+        <v>160</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="F22" s="14" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" s="16">
         <v>12</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="B23" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="C23" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="D23" s="18">
+        <v>5</v>
+      </c>
+      <c r="E23" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="F23" s="17" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" s="13">
         <v>13</v>
       </c>
-      <c r="D8" s="3">
-        <v>150</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="3">
-        <v>4</v>
-      </c>
-      <c r="B9" s="4" t="s">
+      <c r="B24" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C24" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="D24" s="15">
+        <v>50</v>
+      </c>
+      <c r="E24" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="F24" s="14" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25" s="16">
         <v>14</v>
       </c>
-      <c r="C9" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D9" s="3">
-        <v>260</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="3">
-        <v>5</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D10" s="3">
-        <v>210</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="3">
-        <v>6</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D11" s="3">
-        <v>90</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="3">
-        <v>7</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D12" s="3">
+      <c r="B25" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="C25" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="D25" s="18">
+        <v>70</v>
+      </c>
+      <c r="E25" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="F25" s="17" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="B26" s="19"/>
+      <c r="C26" s="19"/>
+      <c r="D26" s="19">
+        <v>2000</v>
+      </c>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="B28" s="20"/>
+      <c r="C28" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="E12" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="3">
-        <v>8</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D13" s="3">
-        <v>40</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="3">
-        <v>9</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D14" s="3">
-        <v>110</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="3">
-        <v>10</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D15" s="3">
-        <v>110</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="3">
-        <v>11</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D16" s="3">
-        <v>160</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="3">
-        <v>12</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="D17" s="3">
-        <v>5</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3">
-        <v>13</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D18" s="3">
-        <v>50</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="3">
-        <v>14</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D19" s="3">
-        <v>70</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>9</v>
-      </c>
+      <c r="D28" s="20"/>
+      <c r="E28" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="F28" s="20"/>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="B29" s="21"/>
+      <c r="C29" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="D29" s="21"/>
+      <c r="E29" s="22"/>
+      <c r="F29" s="22"/>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30" s="21"/>
+      <c r="B30" s="21"/>
+      <c r="C30" s="21"/>
+      <c r="D30" s="21"/>
+      <c r="E30" s="22"/>
+      <c r="F30" s="22"/>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31" s="21"/>
+      <c r="B31" s="21"/>
+      <c r="C31" s="21"/>
+      <c r="D31" s="21"/>
+      <c r="E31" s="23" t="s">
+        <v>63</v>
+      </c>
+      <c r="F31" s="23"/>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32" s="21"/>
+      <c r="B32" s="21"/>
+      <c r="C32" s="21"/>
+      <c r="D32" s="21"/>
+      <c r="E32" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="F32" s="24"/>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34" s="25" t="s">
+        <v>65</v>
+      </c>
+      <c r="B34" s="25"/>
+      <c r="C34" s="25"/>
+      <c r="D34" s="25"/>
+      <c r="E34" s="25"/>
+      <c r="F34" s="25"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <autoFilter ref="A11:F25"/>
+  <mergeCells count="19">
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A29:B32"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="C29:D32"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="E29:F30"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="A34:F34"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.25" right="0.25" top="0.35" bottom="0.35" header="0.3" footer="0.3"/>
+  <pageSetup fitToHeight="0" orientation="landscape"/>
 </worksheet>
 </file>
--- a/backend/app/temp/talep_listesi.xlsx
+++ b/backend/app/temp/talep_listesi.xlsx
@@ -34,10 +34,10 @@
     <t>Rapor Tarihi</t>
   </si>
   <si>
-    <t>07.05.2026 18:49</t>
-  </si>
-  <si>
-    <t>Rapor No: TRL-202605071849</t>
+    <t>07.05.2026 20:53</t>
+  </si>
+  <si>
+    <t>Rapor No: TRL-202605072053</t>
   </si>
   <si>
     <t>KULLANICI FİRMASI</t>
